--- a/data/trans_orig/Q5404-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5404-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>11662</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13076</t>
+          <t>12936</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18786</t>
+          <t>19651</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16371</t>
+          <t>16778</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>9215</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24920</t>
+          <t>24743</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>273032</t>
+          <t>274036</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>287112</t>
+          <t>287203</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>318533</t>
+          <t>318302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>333648</t>
+          <t>333519</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>597266</t>
+          <t>597934</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>617951</t>
+          <t>617306</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>2658</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>11867</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>14044</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34100</t>
+          <t>33282</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18635</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39679</t>
+          <t>41112</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8346</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22484</t>
+          <t>23180</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15837</t>
+          <t>15615</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36104</t>
+          <t>36256</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>27770</t>
+          <t>26883</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52419</t>
+          <t>51848</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>180580</t>
+          <t>179644</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>196556</t>
+          <t>196465</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>272930</t>
+          <t>271017</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>299867</t>
+          <t>299708</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>460022</t>
+          <t>460091</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>491264</t>
+          <t>491205</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,33%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19218</t>
+          <t>18854</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19259</t>
+          <t>19584</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40464</t>
+          <t>40052</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28782</t>
+          <t>28488</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>55118</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29910</t>
+          <t>31579</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24356</t>
+          <t>23392</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47509</t>
+          <t>46644</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42763</t>
+          <t>41076</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70900</t>
+          <t>70642</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>459469</t>
+          <t>458962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>480326</t>
+          <t>479663</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>597520</t>
+          <t>598847</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>628825</t>
+          <t>628560</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1062788</t>
+          <t>1066793</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1102062</t>
+          <t>1104239</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13064</t>
+          <t>12086</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12940</t>
+          <t>12745</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20071</t>
+          <t>21868</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17412</t>
+          <t>17427</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>10964</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26489</t>
+          <t>27273</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17308</t>
+          <t>15890</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38173</t>
+          <t>36610</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>285342</t>
+          <t>287277</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>301862</t>
+          <t>302676</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>319498</t>
+          <t>318989</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>338337</t>
+          <t>338704</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>612884</t>
+          <t>612158</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>636702</t>
+          <t>636999</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t>9624</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27717</t>
+          <t>27114</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29510</t>
+          <t>28828</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54099</t>
+          <t>55495</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43493</t>
+          <t>42763</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73255</t>
+          <t>74412</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14130</t>
+          <t>13833</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33705</t>
+          <t>34119</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44662</t>
+          <t>44759</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73644</t>
+          <t>75462</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>66092</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>102871</t>
+          <t>100067</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>196272</t>
+          <t>196946</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>220883</t>
+          <t>221444</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>270728</t>
+          <t>270174</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>308263</t>
+          <t>306831</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>476851</t>
+          <t>476808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>521642</t>
+          <t>523612</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,96%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13843</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33816</t>
+          <t>36255</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34137</t>
+          <t>32880</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60379</t>
+          <t>60027</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>54167</t>
+          <t>54289</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87626</t>
+          <t>88554</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>18926</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44532</t>
+          <t>43883</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60606</t>
+          <t>58925</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95705</t>
+          <t>94214</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87021</t>
+          <t>87263</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>128747</t>
+          <t>126626</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>490400</t>
+          <t>488971</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>520596</t>
+          <t>520483</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>598491</t>
+          <t>599802</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>639661</t>
+          <t>642328</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1098264</t>
+          <t>1101853</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1152995</t>
+          <t>1151729</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,42%</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>6759</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>7864</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>978</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -4042,12 +4042,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4057,12 +4057,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18311</t>
+          <t>18734</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25076</t>
+          <t>25461</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>320663</t>
+          <t>320362</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>331395</t>
+          <t>331253</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>356970</t>
+          <t>356412</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>370773</t>
+          <t>370797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>681666</t>
+          <t>682123</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>700313</t>
+          <t>699284</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>15226</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17417</t>
+          <t>16970</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41094</t>
+          <t>40877</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24555</t>
+          <t>23435</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51570</t>
+          <t>49979</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -4498,12 +4498,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10621</t>
+          <t>9850</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25509</t>
+          <t>24044</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26402</t>
+          <t>25675</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52465</t>
+          <t>51828</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>40885</t>
+          <t>40424</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>71267</t>
+          <t>71477</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>221976</t>
+          <t>222451</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>239214</t>
+          <t>240219</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>318235</t>
+          <t>318041</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>349901</t>
+          <t>351817</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>547655</t>
+          <t>547619</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>586533</t>
+          <t>584406</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>88,93%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17202</t>
+          <t>17404</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42735</t>
+          <t>43157</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26846</t>
+          <t>26693</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>54224</t>
+          <t>53192</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13687</t>
+          <t>13897</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30963</t>
+          <t>31637</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35940</t>
+          <t>35638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67382</t>
+          <t>64932</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53558</t>
+          <t>55245</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88741</t>
+          <t>89343</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>549165</t>
+          <t>548007</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>568723</t>
+          <t>568650</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>679022</t>
+          <t>679359</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>717207</t>
+          <t>717071</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1240146</t>
+          <t>1236976</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1282104</t>
+          <t>1279168</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>610</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5557,32 +5557,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5592,32 +5592,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -5635,32 +5635,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11900</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5670,32 +5670,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11448</t>
+          <t>12859</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>18694</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5705,32 +5705,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>17783</t>
+          <t>19607</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>13377</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27120</t>
+          <t>27657</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -5748,32 +5748,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>361197</t>
+          <t>399723</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>355750</t>
+          <t>394246</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>364432</t>
+          <t>403076</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>593342</t>
+          <t>422388</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>582418</t>
+          <t>415563</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>602096</t>
+          <t>427346</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5818,32 +5818,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>954540</t>
+          <t>822110</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>944297</t>
+          <t>814146</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>966234</t>
+          <t>829044</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -5861,17 +5861,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5896,17 +5896,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5978,32 +5978,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>13290</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6013,32 +6013,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>34762</t>
+          <t>37497</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26559</t>
+          <t>29499</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44128</t>
+          <t>47985</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>42523</t>
+          <t>45364</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33184</t>
+          <t>36381</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53255</t>
+          <t>56983</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -6091,32 +6091,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25247</t>
+          <t>27494</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17887</t>
+          <t>20563</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34125</t>
+          <t>37612</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6126,32 +6126,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64746</t>
+          <t>69887</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>54780</t>
+          <t>59180</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76401</t>
+          <t>83062</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6161,32 +6161,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>89993</t>
+          <t>97381</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>75956</t>
+          <t>84080</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>103391</t>
+          <t>112321</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -6204,32 +6204,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>249005</t>
+          <t>273951</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>240000</t>
+          <t>263262</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>257189</t>
+          <t>281138</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6239,32 +6239,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>325731</t>
+          <t>356579</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>311398</t>
+          <t>341977</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>337550</t>
+          <t>370567</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6274,32 +6274,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>574736</t>
+          <t>630530</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>558911</t>
+          <t>611521</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>590133</t>
+          <t>646016</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,54%</t>
         </is>
       </c>
     </row>
@@ -6317,17 +6317,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6352,17 +6352,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>425239</t>
+          <t>463963</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>425239</t>
+          <t>463963</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>425239</t>
+          <t>463963</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6387,17 +6387,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>707252</t>
+          <t>773275</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>707252</t>
+          <t>773275</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>707252</t>
+          <t>773275</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6434,32 +6434,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6469,32 +6469,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37930</t>
+          <t>40984</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18716</t>
+          <t>32125</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51530</t>
+          <t>51194</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6504,32 +6504,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>46324</t>
+          <t>49461</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30422</t>
+          <t>39688</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59125</t>
+          <t>60330</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -6547,32 +6547,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31582</t>
+          <t>34242</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23569</t>
+          <t>25678</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41782</t>
+          <t>45234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>76194</t>
+          <t>82746</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37360</t>
+          <t>69870</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99583</t>
+          <t>97847</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6617,32 +6617,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>107776</t>
+          <t>116988</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71708</t>
+          <t>102093</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130360</t>
+          <t>133945</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -6660,32 +6660,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>610202</t>
+          <t>673672</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>598789</t>
+          <t>661824</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>619100</t>
+          <t>683371</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6695,32 +6695,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>919073</t>
+          <t>778968</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>885913</t>
+          <t>762906</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>976059</t>
+          <t>794829</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6730,32 +6730,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1529275</t>
+          <t>1452640</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1499521</t>
+          <t>1433359</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1581375</t>
+          <t>1470580</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>90,83%</t>
         </is>
       </c>
     </row>
@@ -6773,17 +6773,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6808,17 +6808,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1033197</t>
+          <t>902698</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1033197</t>
+          <t>902698</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1033197</t>
+          <t>902698</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1683375</t>
+          <t>1619089</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1683375</t>
+          <t>1619089</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1683375</t>
+          <t>1619089</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
